--- a/Ref docs/Resource/Resource Details - Formatted.xlsx
+++ b/Ref docs/Resource/Resource Details - Formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/anjana_sharma_rockwellautomation_com/Documents/Anjana Sharma - All Important Documents/1. My work/RA Work/AM-APP/Ref docs/Resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BDC3DBC-217A-4C8A-A7A7-D22D2CF37364}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF35C85-39C0-411E-B8B3-32965932097D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3302,7 +3302,7 @@
     <t>Python, .NET , SQL,FastApi, MongoDB ,Azure ,Linux Basics</t>
   </si>
   <si>
-    <t>No Value</t>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -3798,7 +3798,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3850,7 +3849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -3883,7 +3882,7 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3916,7 +3915,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -3943,7 +3942,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -3974,7 +3973,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -4007,7 +4006,7 @@
       </c>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -4075,7 +4074,7 @@
       </c>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -4215,7 +4214,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -4250,7 +4249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -4283,7 +4282,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -4353,7 +4352,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -4388,7 +4387,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -4421,7 +4420,7 @@
       </c>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -4454,7 +4453,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -4489,7 +4488,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -4553,7 +4552,7 @@
       </c>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -4621,7 +4620,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -4656,7 +4655,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -4683,7 +4682,7 @@
       </c>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -4858,7 +4857,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -4889,7 +4888,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -4959,7 +4958,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4992,7 +4991,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -5027,7 +5026,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -5060,7 +5059,7 @@
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5095,7 +5094,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5128,7 +5127,7 @@
       </c>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5163,7 +5162,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5198,7 +5197,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5231,7 +5230,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5295,7 +5294,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5398,7 +5397,7 @@
       </c>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5433,7 +5432,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5503,7 +5502,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5532,7 +5531,7 @@
       </c>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5602,7 +5601,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -5635,7 +5634,7 @@
       </c>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5668,7 +5667,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5703,7 +5702,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5738,7 +5737,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -5872,7 +5871,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5899,7 +5898,7 @@
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -5934,7 +5933,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -5963,7 +5962,7 @@
       </c>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -5994,7 +5993,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6060,7 +6059,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -6095,7 +6094,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -6126,7 +6125,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -6161,7 +6160,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -6196,7 +6195,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -6229,7 +6228,7 @@
       </c>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -6262,7 +6261,7 @@
       </c>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -6367,7 +6366,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -6402,7 +6401,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -6433,7 +6432,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -6468,7 +6467,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -6538,7 +6537,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -6571,7 +6570,7 @@
       </c>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -6606,7 +6605,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -6641,7 +6640,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -6672,7 +6671,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -6707,7 +6706,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -6738,7 +6737,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -6773,7 +6772,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -6843,7 +6842,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -6876,7 +6875,7 @@
       </c>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -6909,7 +6908,7 @@
       </c>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -6944,7 +6943,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -6979,7 +6978,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7012,7 +7011,7 @@
       </c>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -7082,7 +7081,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -7146,7 +7145,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -7181,7 +7180,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -7214,7 +7213,7 @@
       </c>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -7284,7 +7283,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -7319,7 +7318,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -7354,7 +7353,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -7389,7 +7388,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -7422,7 +7421,7 @@
       </c>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -7455,7 +7454,7 @@
       </c>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -7488,7 +7487,7 @@
       </c>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -7521,7 +7520,7 @@
       </c>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -7552,7 +7551,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -7581,7 +7580,7 @@
       </c>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -7616,7 +7615,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -7649,7 +7648,7 @@
       </c>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -7684,7 +7683,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -7719,7 +7718,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -7750,7 +7749,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -7816,7 +7815,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -7851,7 +7850,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -7886,7 +7885,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -7921,7 +7920,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -7956,7 +7955,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -7989,7 +7988,7 @@
       </c>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -8024,7 +8023,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -8059,7 +8058,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -8092,7 +8091,7 @@
       </c>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -8127,7 +8126,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -8162,7 +8161,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -8228,7 +8227,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -8263,7 +8262,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -8298,7 +8297,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -8331,7 +8330,7 @@
       </c>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -8399,7 +8398,7 @@
       </c>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -8432,7 +8431,7 @@
       </c>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -8465,7 +8464,7 @@
       </c>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -8498,7 +8497,7 @@
       </c>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -8533,7 +8532,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -8568,7 +8567,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -8603,7 +8602,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -8638,7 +8637,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -8673,7 +8672,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -8741,7 +8740,7 @@
       </c>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -8772,7 +8771,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -8807,7 +8806,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -8842,7 +8841,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -8877,7 +8876,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -8912,7 +8911,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -8976,7 +8975,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -9011,7 +9010,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -9044,7 +9043,7 @@
       </c>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -9079,7 +9078,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -9112,7 +9111,7 @@
       </c>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -9147,7 +9146,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -9211,7 +9210,7 @@
       </c>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -9246,7 +9245,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -9279,7 +9278,7 @@
       </c>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -9308,7 +9307,7 @@
       </c>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -9339,7 +9338,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -9372,7 +9371,7 @@
       </c>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -9407,7 +9406,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -9440,7 +9439,7 @@
       </c>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -9475,7 +9474,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -9510,7 +9509,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -9545,7 +9544,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -9578,7 +9577,7 @@
       </c>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>171</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>172</v>
       </c>
@@ -9646,7 +9645,7 @@
       </c>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>173</v>
       </c>
@@ -9679,7 +9678,7 @@
       </c>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>174</v>
       </c>
@@ -9712,7 +9711,7 @@
       </c>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>175</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>176</v>
       </c>
@@ -9776,7 +9775,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>177</v>
       </c>
@@ -9811,7 +9810,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>178</v>
       </c>
@@ -9846,7 +9845,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>179</v>
       </c>
@@ -9881,7 +9880,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>180</v>
       </c>
@@ -9914,7 +9913,7 @@
       </c>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>181</v>
       </c>
@@ -9945,7 +9944,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>182</v>
       </c>
@@ -9980,7 +9979,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -10015,7 +10014,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -10050,7 +10049,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -10081,7 +10080,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -10116,7 +10115,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -10151,7 +10150,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -10186,7 +10185,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -10256,7 +10255,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -10316,7 +10315,7 @@
       </c>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -10351,7 +10350,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -10382,7 +10381,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -10417,7 +10416,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -10452,7 +10451,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -10487,7 +10486,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -10522,7 +10521,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -10557,7 +10556,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -10592,7 +10591,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -10627,7 +10626,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -10662,7 +10661,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -10732,7 +10731,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -10765,7 +10764,7 @@
       </c>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -10796,7 +10795,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -10866,7 +10865,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -10901,7 +10900,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -10936,7 +10935,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -11002,7 +11001,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -11037,7 +11036,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -11072,7 +11071,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -11103,7 +11102,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -11138,7 +11137,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -11173,7 +11172,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -11241,7 +11240,7 @@
       </c>
       <c r="K220" s="6"/>
     </row>
-    <row r="221" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -11276,7 +11275,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -11311,7 +11310,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -11344,7 +11343,7 @@
       </c>
       <c r="K223" s="6"/>
     </row>
-    <row r="224" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -11377,7 +11376,7 @@
       </c>
       <c r="K224" s="6"/>
     </row>
-    <row r="225" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -11404,7 +11403,7 @@
       </c>
       <c r="K225" s="6"/>
     </row>
-    <row r="226" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>225</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>226</v>
       </c>
@@ -11474,7 +11473,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>227</v>
       </c>
@@ -11509,7 +11508,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>228</v>
       </c>
@@ -11542,7 +11541,7 @@
       </c>
       <c r="K229" s="6"/>
     </row>
-    <row r="230" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>229</v>
       </c>
@@ -11569,7 +11568,7 @@
       </c>
       <c r="K230" s="6"/>
     </row>
-    <row r="231" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>230</v>
       </c>
@@ -11604,7 +11603,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>231</v>
       </c>
@@ -11639,7 +11638,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>232</v>
       </c>
@@ -11674,7 +11673,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>233</v>
       </c>
@@ -11707,7 +11706,7 @@
       </c>
       <c r="K234" s="6"/>
     </row>
-    <row r="235" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -11740,7 +11739,7 @@
       </c>
       <c r="K235" s="6"/>
     </row>
-    <row r="236" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>235</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>236</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>237</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>238</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>239</v>
       </c>
@@ -11913,7 +11912,7 @@
       </c>
       <c r="K240" s="6"/>
     </row>
-    <row r="241" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>240</v>
       </c>
@@ -11948,7 +11947,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>241</v>
       </c>
@@ -11983,7 +11982,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>242</v>
       </c>
@@ -12016,7 +12015,7 @@
       </c>
       <c r="K243" s="6"/>
     </row>
-    <row r="244" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>243</v>
       </c>
@@ -12051,7 +12050,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>244</v>
       </c>
@@ -12086,7 +12085,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>245</v>
       </c>
@@ -12119,7 +12118,7 @@
       </c>
       <c r="K246" s="6"/>
     </row>
-    <row r="247" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>246</v>
       </c>
@@ -12154,7 +12153,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>247</v>
       </c>
@@ -12189,7 +12188,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>248</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>249</v>
       </c>
@@ -12255,7 +12254,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>250</v>
       </c>
@@ -12290,7 +12289,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>251</v>
       </c>
@@ -12323,7 +12322,7 @@
       </c>
       <c r="K252" s="6"/>
     </row>
-    <row r="253" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>252</v>
       </c>
@@ -12358,7 +12357,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -12393,7 +12392,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -12428,7 +12427,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -12492,7 +12491,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -12527,7 +12526,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -12562,7 +12561,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -12595,7 +12594,7 @@
       </c>
       <c r="K260" s="6"/>
     </row>
-    <row r="261" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -12628,7 +12627,7 @@
       </c>
       <c r="K261" s="6"/>
     </row>
-    <row r="262" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -12663,7 +12662,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -12698,7 +12697,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -12731,7 +12730,7 @@
       </c>
       <c r="K264" s="6"/>
     </row>
-    <row r="265" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -12766,7 +12765,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -12795,7 +12794,7 @@
       </c>
       <c r="K266" s="6"/>
     </row>
-    <row r="267" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -12830,7 +12829,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -12861,7 +12860,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -12896,7 +12895,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -12929,7 +12928,7 @@
       </c>
       <c r="K270" s="6"/>
     </row>
-    <row r="271" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -12964,7 +12963,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -12997,7 +12996,7 @@
       </c>
       <c r="K272" s="6"/>
     </row>
-    <row r="273" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -13032,7 +13031,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -13059,7 +13058,7 @@
       </c>
       <c r="K274" s="6"/>
     </row>
-    <row r="275" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -13094,7 +13093,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -13129,7 +13128,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -13164,7 +13163,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -13193,7 +13192,7 @@
       </c>
       <c r="K278" s="6"/>
     </row>
-    <row r="279" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -13259,7 +13258,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -13292,7 +13291,7 @@
       </c>
       <c r="K281" s="6"/>
     </row>
-    <row r="282" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -13323,7 +13322,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -13385,7 +13384,7 @@
       </c>
       <c r="K284" s="6"/>
     </row>
-    <row r="285" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -13413,7 +13412,7 @@
       <c r="I285" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J285" s="7" t="s">
+      <c r="J285" s="1" t="s">
         <v>1088</v>
       </c>
       <c r="K285" s="8" t="s">
@@ -13421,13 +13420,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="126.42 years"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Ref docs/Resource/Resource Details - Formatted.xlsx
+++ b/Ref docs/Resource/Resource Details - Formatted.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/anjana_sharma_rockwellautomation_com/Documents/Anjana Sharma - All Important Documents/1. My work/RA Work/AM-APP/Ref docs/Resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF35C85-39C0-411E-B8B3-32965932097D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CCDBEE-9E4F-4934-9346-352174D47DA6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3798,6 +3798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3849,7 +3850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -3882,7 +3883,7 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3915,7 +3916,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -3942,7 +3943,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v>38</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>39</v>
+        <v>699</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>1088</v>
@@ -4041,7 +4042,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -4074,7 +4075,7 @@
       </c>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -4109,7 +4110,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -4214,7 +4215,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -4249,7 +4250,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -4282,7 +4283,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -4317,7 +4318,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -4352,7 +4353,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -4387,7 +4388,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -4420,7 +4421,7 @@
       </c>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -4453,7 +4454,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -4519,7 +4520,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -4552,7 +4553,7 @@
       </c>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -4587,7 +4588,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -4620,7 +4621,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -4655,7 +4656,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -4682,7 +4683,7 @@
       </c>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -4717,7 +4718,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -4752,7 +4753,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -4787,7 +4788,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -4822,7 +4823,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -4923,7 +4924,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -4958,7 +4959,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4991,7 +4992,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -5026,7 +5027,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -5059,7 +5060,7 @@
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5094,7 +5095,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5127,7 +5128,7 @@
       </c>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5162,7 +5163,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5197,7 +5198,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5230,7 +5231,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5329,7 +5330,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5364,7 +5365,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5397,7 +5398,7 @@
       </c>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5432,7 +5433,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -5467,7 +5468,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5531,7 +5532,7 @@
       </c>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5566,7 +5567,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -5634,7 +5635,7 @@
       </c>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5667,7 +5668,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5702,7 +5703,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5737,7 +5738,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5772,7 +5773,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -5805,7 +5806,7 @@
       </c>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -5840,7 +5841,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -5871,7 +5872,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5898,7 +5899,7 @@
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -5933,7 +5934,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -5962,7 +5963,7 @@
       </c>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -5993,7 +5994,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6059,7 +6060,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -6094,7 +6095,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -6125,7 +6126,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -6160,7 +6161,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -6195,7 +6196,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -6228,7 +6229,7 @@
       </c>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -6261,7 +6262,7 @@
       </c>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -6331,7 +6332,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -6366,7 +6367,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -6401,7 +6402,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -6432,7 +6433,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -6467,7 +6468,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -6502,7 +6503,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -6537,7 +6538,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -6570,7 +6571,7 @@
       </c>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -6605,7 +6606,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -6640,7 +6641,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -6671,7 +6672,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -6706,7 +6707,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -6772,7 +6773,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -6875,7 +6876,7 @@
       </c>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -6908,7 +6909,7 @@
       </c>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -6943,7 +6944,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -6978,7 +6979,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7011,7 +7012,7 @@
       </c>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -7046,7 +7047,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -7081,7 +7082,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -7116,7 +7117,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -7145,7 +7146,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -7213,7 +7214,7 @@
       </c>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -7388,7 +7389,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -7421,7 +7422,7 @@
       </c>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -7454,7 +7455,7 @@
       </c>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -7487,7 +7488,7 @@
       </c>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -7520,7 +7521,7 @@
       </c>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -7551,7 +7552,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -7580,7 +7581,7 @@
       </c>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -7615,7 +7616,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -7648,7 +7649,7 @@
       </c>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -7683,7 +7684,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -7718,7 +7719,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -7749,7 +7750,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -7784,7 +7785,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -7815,7 +7816,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -7850,7 +7851,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -7920,7 +7921,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -7988,7 +7989,7 @@
       </c>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -8058,7 +8059,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -8091,7 +8092,7 @@
       </c>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -8126,7 +8127,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -8161,7 +8162,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -8227,7 +8228,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -8262,7 +8263,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -8297,7 +8298,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -8330,7 +8331,7 @@
       </c>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -8398,7 +8399,7 @@
       </c>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -8431,7 +8432,7 @@
       </c>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -8464,7 +8465,7 @@
       </c>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -8497,7 +8498,7 @@
       </c>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -8532,7 +8533,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -8567,7 +8568,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -8602,7 +8603,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -8672,7 +8673,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -8707,7 +8708,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -8740,7 +8741,7 @@
       </c>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -8771,7 +8772,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -8806,7 +8807,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -8841,7 +8842,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -8876,7 +8877,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -8911,7 +8912,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -8940,7 +8941,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -8975,7 +8976,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -9010,7 +9011,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -9043,7 +9044,7 @@
       </c>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -9078,7 +9079,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -9111,7 +9112,7 @@
       </c>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -9146,7 +9147,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -9181,7 +9182,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -9210,7 +9211,7 @@
       </c>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -9245,7 +9246,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -9278,7 +9279,7 @@
       </c>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -9307,7 +9308,7 @@
       </c>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -9338,7 +9339,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -9371,7 +9372,7 @@
       </c>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -9406,7 +9407,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -9439,7 +9440,7 @@
       </c>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -9474,7 +9475,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -9509,7 +9510,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -9544,7 +9545,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -9577,7 +9578,7 @@
       </c>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>171</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>172</v>
       </c>
@@ -9645,7 +9646,7 @@
       </c>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>173</v>
       </c>
@@ -9678,7 +9679,7 @@
       </c>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>174</v>
       </c>
@@ -9711,7 +9712,7 @@
       </c>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>175</v>
       </c>
@@ -9740,7 +9741,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>176</v>
       </c>
@@ -9775,7 +9776,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>177</v>
       </c>
@@ -9810,7 +9811,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>178</v>
       </c>
@@ -9845,7 +9846,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>179</v>
       </c>
@@ -9880,7 +9881,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>180</v>
       </c>
@@ -9913,7 +9914,7 @@
       </c>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>181</v>
       </c>
@@ -9944,7 +9945,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>182</v>
       </c>
@@ -9979,7 +9980,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -10014,7 +10015,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -10049,7 +10050,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -10080,7 +10081,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -10115,7 +10116,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -10150,7 +10151,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -10185,7 +10186,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -10220,7 +10221,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -10255,7 +10256,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -10288,7 +10289,7 @@
       </c>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -10315,7 +10316,7 @@
       </c>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -10350,7 +10351,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -10381,7 +10382,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -10416,7 +10417,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -10451,7 +10452,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -10521,7 +10522,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -10556,7 +10557,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -10591,7 +10592,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -10626,7 +10627,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -10661,7 +10662,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -10696,7 +10697,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -10731,7 +10732,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -10764,7 +10765,7 @@
       </c>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -10795,7 +10796,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -10865,7 +10866,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -10900,7 +10901,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -10935,7 +10936,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -10966,7 +10967,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -11001,7 +11002,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -11036,7 +11037,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -11071,7 +11072,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -11102,7 +11103,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -11137,7 +11138,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -11172,7 +11173,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -11207,7 +11208,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -11240,7 +11241,7 @@
       </c>
       <c r="K220" s="6"/>
     </row>
-    <row r="221" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -11275,7 +11276,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -11310,7 +11311,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -11343,7 +11344,7 @@
       </c>
       <c r="K223" s="6"/>
     </row>
-    <row r="224" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -11376,7 +11377,7 @@
       </c>
       <c r="K224" s="6"/>
     </row>
-    <row r="225" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -11403,7 +11404,7 @@
       </c>
       <c r="K225" s="6"/>
     </row>
-    <row r="226" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>225</v>
       </c>
@@ -11438,7 +11439,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>226</v>
       </c>
@@ -11473,7 +11474,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>227</v>
       </c>
@@ -11508,7 +11509,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>228</v>
       </c>
@@ -11541,7 +11542,7 @@
       </c>
       <c r="K229" s="6"/>
     </row>
-    <row r="230" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>229</v>
       </c>
@@ -11568,7 +11569,7 @@
       </c>
       <c r="K230" s="6"/>
     </row>
-    <row r="231" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>230</v>
       </c>
@@ -11603,7 +11604,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>231</v>
       </c>
@@ -11638,7 +11639,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>232</v>
       </c>
@@ -11673,7 +11674,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>233</v>
       </c>
@@ -11706,7 +11707,7 @@
       </c>
       <c r="K234" s="6"/>
     </row>
-    <row r="235" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -11739,7 +11740,7 @@
       </c>
       <c r="K235" s="6"/>
     </row>
-    <row r="236" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>235</v>
       </c>
@@ -11774,7 +11775,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>236</v>
       </c>
@@ -11809,7 +11810,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>237</v>
       </c>
@@ -11844,7 +11845,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>238</v>
       </c>
@@ -11879,7 +11880,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>239</v>
       </c>
@@ -11912,7 +11913,7 @@
       </c>
       <c r="K240" s="6"/>
     </row>
-    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>240</v>
       </c>
@@ -11947,7 +11948,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>241</v>
       </c>
@@ -11982,7 +11983,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>242</v>
       </c>
@@ -12015,7 +12016,7 @@
       </c>
       <c r="K243" s="6"/>
     </row>
-    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>243</v>
       </c>
@@ -12050,7 +12051,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>244</v>
       </c>
@@ -12085,7 +12086,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>245</v>
       </c>
@@ -12118,7 +12119,7 @@
       </c>
       <c r="K246" s="6"/>
     </row>
-    <row r="247" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>246</v>
       </c>
@@ -12153,7 +12154,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>247</v>
       </c>
@@ -12188,7 +12189,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>248</v>
       </c>
@@ -12219,7 +12220,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>249</v>
       </c>
@@ -12254,7 +12255,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>250</v>
       </c>
@@ -12289,7 +12290,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>251</v>
       </c>
@@ -12322,7 +12323,7 @@
       </c>
       <c r="K252" s="6"/>
     </row>
-    <row r="253" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>252</v>
       </c>
@@ -12357,7 +12358,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -12392,7 +12393,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -12427,7 +12428,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -12460,7 +12461,7 @@
       </c>
       <c r="K256" s="6"/>
     </row>
-    <row r="257" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -12491,7 +12492,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -12526,7 +12527,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -12561,7 +12562,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -12594,7 +12595,7 @@
       </c>
       <c r="K260" s="6"/>
     </row>
-    <row r="261" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -12627,7 +12628,7 @@
       </c>
       <c r="K261" s="6"/>
     </row>
-    <row r="262" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -12662,7 +12663,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -12697,7 +12698,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -12730,7 +12731,7 @@
       </c>
       <c r="K264" s="6"/>
     </row>
-    <row r="265" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -12765,7 +12766,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -12794,7 +12795,7 @@
       </c>
       <c r="K266" s="6"/>
     </row>
-    <row r="267" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -12829,7 +12830,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -12860,7 +12861,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -12895,7 +12896,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -12928,7 +12929,7 @@
       </c>
       <c r="K270" s="6"/>
     </row>
-    <row r="271" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -12963,7 +12964,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -12996,7 +12997,7 @@
       </c>
       <c r="K272" s="6"/>
     </row>
-    <row r="273" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -13031,7 +13032,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -13058,7 +13059,7 @@
       </c>
       <c r="K274" s="6"/>
     </row>
-    <row r="275" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -13093,7 +13094,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -13128,7 +13129,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -13163,7 +13164,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -13192,7 +13193,7 @@
       </c>
       <c r="K278" s="6"/>
     </row>
-    <row r="279" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -13223,7 +13224,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -13258,7 +13259,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -13291,7 +13292,7 @@
       </c>
       <c r="K281" s="6"/>
     </row>
-    <row r="282" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -13322,7 +13323,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -13357,7 +13358,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -13384,7 +13385,7 @@
       </c>
       <c r="K284" s="6"/>
     </row>
-    <row r="285" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -13420,7 +13421,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Abhishek Kurup"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Ref docs/Resource/Resource Details - Formatted.xlsx
+++ b/Ref docs/Resource/Resource Details - Formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockwellautomation-my.sharepoint.com/personal/anjana_sharma_rockwellautomation_com/Documents/Anjana Sharma - All Important Documents/1. My work/RA Work/AM-APP/Ref docs/Resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CCDBEE-9E4F-4934-9346-352174D47DA6}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{B2E8D8F5-9C64-446D-9463-DBC50913925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{120D0C35-B10B-4B47-8C9F-E73C70C5F61A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3798,7 +3798,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3850,7 +3849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -3883,7 +3882,7 @@
       </c>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3916,7 +3915,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -3943,7 +3942,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -3974,7 +3973,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -4042,7 +4041,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -4075,7 +4074,7 @@
       </c>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -4180,7 +4179,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -4215,7 +4214,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -4250,7 +4249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -4283,7 +4282,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -4353,7 +4352,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -4388,7 +4387,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -4421,7 +4420,7 @@
       </c>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -4454,7 +4453,7 @@
       </c>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -4489,7 +4488,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -4553,7 +4552,7 @@
       </c>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -4621,7 +4620,7 @@
       </c>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -4656,7 +4655,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -4683,7 +4682,7 @@
       </c>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -4823,7 +4822,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -4858,7 +4857,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -4889,7 +4888,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -4959,7 +4958,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4992,7 +4991,7 @@
       </c>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -5027,7 +5026,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -5060,7 +5059,7 @@
       </c>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5095,7 +5094,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5128,7 +5127,7 @@
       </c>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5163,7 +5162,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5198,7 +5197,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5231,7 +5230,7 @@
       </c>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5260,7 +5259,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5295,7 +5294,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5330,7 +5329,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5365,7 +5364,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5398,7 +5397,7 @@
       </c>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5433,7 +5432,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -5503,7 +5502,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5532,7 +5531,7 @@
       </c>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -5602,7 +5601,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -5635,7 +5634,7 @@
       </c>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5668,7 +5667,7 @@
       </c>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5703,7 +5702,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5738,7 +5737,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -5806,7 +5805,7 @@
       </c>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -5872,7 +5871,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -5899,7 +5898,7 @@
       </c>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -5934,7 +5933,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -5963,7 +5962,7 @@
       </c>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -5994,7 +5993,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6060,7 +6059,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -6095,7 +6094,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -6126,7 +6125,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -6161,7 +6160,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -6196,7 +6195,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -6229,7 +6228,7 @@
       </c>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -6262,7 +6261,7 @@
       </c>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -6367,7 +6366,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -6402,7 +6401,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -6433,7 +6432,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -6468,7 +6467,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -6503,7 +6502,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -6538,7 +6537,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -6571,7 +6570,7 @@
       </c>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -6606,7 +6605,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -6641,7 +6640,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -6672,7 +6671,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -6707,7 +6706,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -6738,7 +6737,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -6773,7 +6772,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -6843,7 +6842,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -6876,7 +6875,7 @@
       </c>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -6909,7 +6908,7 @@
       </c>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -6944,7 +6943,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -6979,7 +6978,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7012,7 +7011,7 @@
       </c>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -7082,7 +7081,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -7146,7 +7145,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -7181,7 +7180,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -7214,7 +7213,7 @@
       </c>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -7284,7 +7283,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -7319,7 +7318,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -7354,7 +7353,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -7389,7 +7388,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -7422,7 +7421,7 @@
       </c>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -7455,7 +7454,7 @@
       </c>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -7488,7 +7487,7 @@
       </c>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -7521,7 +7520,7 @@
       </c>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -7552,7 +7551,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -7581,7 +7580,7 @@
       </c>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -7616,7 +7615,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -7649,7 +7648,7 @@
       </c>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -7684,7 +7683,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -7719,7 +7718,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -7750,7 +7749,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -7816,7 +7815,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -7851,7 +7850,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -7886,7 +7885,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -7921,7 +7920,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -7956,7 +7955,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -7989,7 +7988,7 @@
       </c>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -8024,7 +8023,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -8059,7 +8058,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -8092,7 +8091,7 @@
       </c>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -8127,7 +8126,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -8162,7 +8161,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -8197,7 +8196,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -8228,7 +8227,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -8263,7 +8262,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -8298,7 +8297,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -8331,7 +8330,7 @@
       </c>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -8366,7 +8365,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -8399,7 +8398,7 @@
       </c>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -8432,7 +8431,7 @@
       </c>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -8465,7 +8464,7 @@
       </c>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -8498,7 +8497,7 @@
       </c>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -8533,7 +8532,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -8568,7 +8567,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -8603,7 +8602,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -8638,7 +8637,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -8673,7 +8672,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -8741,7 +8740,7 @@
       </c>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -8772,7 +8771,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -8807,7 +8806,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -8842,7 +8841,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -8877,7 +8876,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -8912,7 +8911,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -8976,7 +8975,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -9011,7 +9010,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -9044,7 +9043,7 @@
       </c>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -9079,7 +9078,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -9112,7 +9111,7 @@
       </c>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -9147,7 +9146,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -9182,7 +9181,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -9211,7 +9210,7 @@
       </c>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -9246,7 +9245,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -9279,7 +9278,7 @@
       </c>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -9308,7 +9307,7 @@
       </c>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -9339,7 +9338,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -9372,7 +9371,7 @@
       </c>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -9407,7 +9406,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -9440,7 +9439,7 @@
       </c>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -9475,7 +9474,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -9510,7 +9509,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -9545,7 +9544,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -9578,7 +9577,7 @@
       </c>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>171</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>172</v>
       </c>
@@ -9646,7 +9645,7 @@
       </c>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>173</v>
       </c>
@@ -9679,7 +9678,7 @@
       </c>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>174</v>
       </c>
@@ -9712,7 +9711,7 @@
       </c>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>175</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>176</v>
       </c>
@@ -9776,7 +9775,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>177</v>
       </c>
@@ -9811,7 +9810,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>178</v>
       </c>
@@ -9846,7 +9845,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>179</v>
       </c>
@@ -9881,7 +9880,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>180</v>
       </c>
@@ -9914,7 +9913,7 @@
       </c>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>181</v>
       </c>
@@ -9945,7 +9944,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>182</v>
       </c>
@@ -9980,7 +9979,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>183</v>
       </c>
@@ -10015,7 +10014,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>184</v>
       </c>
@@ -10050,7 +10049,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>185</v>
       </c>
@@ -10081,7 +10080,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>186</v>
       </c>
@@ -10116,7 +10115,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>187</v>
       </c>
@@ -10151,7 +10150,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>188</v>
       </c>
@@ -10186,7 +10185,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>189</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>190</v>
       </c>
@@ -10256,7 +10255,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>191</v>
       </c>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>192</v>
       </c>
@@ -10316,7 +10315,7 @@
       </c>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>193</v>
       </c>
@@ -10351,7 +10350,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>194</v>
       </c>
@@ -10382,7 +10381,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>195</v>
       </c>
@@ -10417,7 +10416,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>196</v>
       </c>
@@ -10452,7 +10451,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>197</v>
       </c>
@@ -10487,7 +10486,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>198</v>
       </c>
@@ -10522,7 +10521,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>199</v>
       </c>
@@ -10557,7 +10556,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>200</v>
       </c>
@@ -10592,7 +10591,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>201</v>
       </c>
@@ -10627,7 +10626,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>202</v>
       </c>
@@ -10662,7 +10661,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>203</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>204</v>
       </c>
@@ -10732,7 +10731,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>205</v>
       </c>
@@ -10765,7 +10764,7 @@
       </c>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>206</v>
       </c>
@@ -10796,7 +10795,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>207</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>208</v>
       </c>
@@ -10866,7 +10865,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>209</v>
       </c>
@@ -10901,7 +10900,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>210</v>
       </c>
@@ -10936,7 +10935,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>211</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>212</v>
       </c>
@@ -11002,7 +11001,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>213</v>
       </c>
@@ -11037,7 +11036,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>214</v>
       </c>
@@ -11072,7 +11071,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>215</v>
       </c>
@@ -11103,7 +11102,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>216</v>
       </c>
@@ -11138,7 +11137,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>217</v>
       </c>
@@ -11173,7 +11172,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>218</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>219</v>
       </c>
@@ -11241,7 +11240,7 @@
       </c>
       <c r="K220" s="6"/>
     </row>
-    <row r="221" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>220</v>
       </c>
@@ -11276,7 +11275,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>221</v>
       </c>
@@ -11311,7 +11310,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>222</v>
       </c>
@@ -11344,7 +11343,7 @@
       </c>
       <c r="K223" s="6"/>
     </row>
-    <row r="224" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -11377,7 +11376,7 @@
       </c>
       <c r="K224" s="6"/>
     </row>
-    <row r="225" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>224</v>
       </c>
@@ -11404,7 +11403,7 @@
       </c>
       <c r="K225" s="6"/>
     </row>
-    <row r="226" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>225</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>226</v>
       </c>
@@ -11474,7 +11473,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>227</v>
       </c>
@@ -11509,7 +11508,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>228</v>
       </c>
@@ -11542,7 +11541,7 @@
       </c>
       <c r="K229" s="6"/>
     </row>
-    <row r="230" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>229</v>
       </c>
@@ -11569,7 +11568,7 @@
       </c>
       <c r="K230" s="6"/>
     </row>
-    <row r="231" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>230</v>
       </c>
@@ -11604,7 +11603,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>231</v>
       </c>
@@ -11639,7 +11638,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>232</v>
       </c>
@@ -11674,7 +11673,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>233</v>
       </c>
@@ -11707,7 +11706,7 @@
       </c>
       <c r="K234" s="6"/>
     </row>
-    <row r="235" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>234</v>
       </c>
@@ -11740,7 +11739,7 @@
       </c>
       <c r="K235" s="6"/>
     </row>
-    <row r="236" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>235</v>
       </c>
@@ -11775,7 +11774,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>236</v>
       </c>
@@ -11810,7 +11809,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>237</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>238</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>239</v>
       </c>
@@ -11913,7 +11912,7 @@
       </c>
       <c r="K240" s="6"/>
     </row>
-    <row r="241" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>240</v>
       </c>
@@ -11948,7 +11947,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>241</v>
       </c>
@@ -11983,7 +11982,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>242</v>
       </c>
@@ -12016,7 +12015,7 @@
       </c>
       <c r="K243" s="6"/>
     </row>
-    <row r="244" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>243</v>
       </c>
@@ -12051,7 +12050,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>244</v>
       </c>
@@ -12086,7 +12085,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>245</v>
       </c>
@@ -12119,7 +12118,7 @@
       </c>
       <c r="K246" s="6"/>
     </row>
-    <row r="247" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>246</v>
       </c>
@@ -12154,7 +12153,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>247</v>
       </c>
@@ -12189,7 +12188,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>248</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>249</v>
       </c>
@@ -12255,7 +12254,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>250</v>
       </c>
@@ -12290,7 +12289,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>251</v>
       </c>
@@ -12323,7 +12322,7 @@
       </c>
       <c r="K252" s="6"/>
     </row>
-    <row r="253" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>252</v>
       </c>
@@ -12358,7 +12357,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>253</v>
       </c>
@@ -12393,7 +12392,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>254</v>
       </c>
@@ -12428,7 +12427,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>255</v>
       </c>
@@ -12461,7 +12460,7 @@
       </c>
       <c r="K256" s="6"/>
     </row>
-    <row r="257" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="5">
         <v>256</v>
       </c>
@@ -12492,7 +12491,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>257</v>
       </c>
@@ -12527,7 +12526,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>258</v>
       </c>
@@ -12562,7 +12561,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>259</v>
       </c>
@@ -12595,7 +12594,7 @@
       </c>
       <c r="K260" s="6"/>
     </row>
-    <row r="261" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>260</v>
       </c>
@@ -12628,7 +12627,7 @@
       </c>
       <c r="K261" s="6"/>
     </row>
-    <row r="262" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>261</v>
       </c>
@@ -12663,7 +12662,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>262</v>
       </c>
@@ -12698,7 +12697,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>263</v>
       </c>
@@ -12731,7 +12730,7 @@
       </c>
       <c r="K264" s="6"/>
     </row>
-    <row r="265" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>264</v>
       </c>
@@ -12766,7 +12765,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>265</v>
       </c>
@@ -12795,7 +12794,7 @@
       </c>
       <c r="K266" s="6"/>
     </row>
-    <row r="267" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>266</v>
       </c>
@@ -12830,7 +12829,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>267</v>
       </c>
@@ -12861,7 +12860,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>268</v>
       </c>
@@ -12896,7 +12895,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>269</v>
       </c>
@@ -12929,7 +12928,7 @@
       </c>
       <c r="K270" s="6"/>
     </row>
-    <row r="271" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>270</v>
       </c>
@@ -12964,7 +12963,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>271</v>
       </c>
@@ -12997,7 +12996,7 @@
       </c>
       <c r="K272" s="6"/>
     </row>
-    <row r="273" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>272</v>
       </c>
@@ -13032,7 +13031,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>273</v>
       </c>
@@ -13059,7 +13058,7 @@
       </c>
       <c r="K274" s="6"/>
     </row>
-    <row r="275" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>274</v>
       </c>
@@ -13094,7 +13093,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>275</v>
       </c>
@@ -13129,7 +13128,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>276</v>
       </c>
@@ -13164,7 +13163,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>277</v>
       </c>
@@ -13193,7 +13192,7 @@
       </c>
       <c r="K278" s="6"/>
     </row>
-    <row r="279" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>278</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>279</v>
       </c>
@@ -13259,7 +13258,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>280</v>
       </c>
@@ -13292,7 +13291,7 @@
       </c>
       <c r="K281" s="6"/>
     </row>
-    <row r="282" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>281</v>
       </c>
@@ -13323,7 +13322,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>282</v>
       </c>
@@ -13358,7 +13357,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>283</v>
       </c>
@@ -13385,7 +13384,7 @@
       </c>
       <c r="K284" s="6"/>
     </row>
-    <row r="285" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>284</v>
       </c>
@@ -13421,13 +13420,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Abhishek Kurup"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K285" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>